--- a/src/views/game/zlzq/cardList/akuiCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/akuiCard/z_level.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13665" windowHeight="9975" activeTab="1"/>
+    <workbookView windowWidth="10080" windowHeight="10710" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -64,15 +64,15 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
-  </si>
-  <si>
     <t>四芒军旗</t>
   </si>
   <si>
     <t>热血冒险家</t>
   </si>
   <si>
+    <t>符文·民兵集结</t>
+  </si>
+  <si>
     <t>白袍主教</t>
   </si>
   <si>
@@ -121,12 +121,12 @@
     <t>心灵黑洞2</t>
   </si>
   <si>
+    <t>黑夜突袭</t>
+  </si>
+  <si>
     <t>狡诈学徒</t>
   </si>
   <si>
-    <t>黑夜突袭</t>
-  </si>
-  <si>
     <t>酗酒醉汉</t>
   </si>
   <si>
@@ -175,9 +175,6 @@
     <t>强行捕猎</t>
   </si>
   <si>
-    <t>无畏猎户</t>
-  </si>
-  <si>
     <t>诱敌草人</t>
   </si>
   <si>
@@ -185,6 +182,9 @@
   </si>
   <si>
     <t>活力仙人掌</t>
+  </si>
+  <si>
+    <t>地洞巨獾</t>
   </si>
   <si>
     <t>飞斧狂人</t>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1271,10 +1271,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1285,7 +1285,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1318,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1329,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C11:C17)</f>
-        <v>21.1428571428571</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1362,7 +1362,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1395,7 +1395,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1406,7 +1406,7 @@
         <v>6</v>
       </c>
       <c r="C27" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C31" s="3">
         <f>AVERAGE(C23:C28)</f>
-        <v>21.8333333333333</v>
+        <v>22.3333333333333</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -1451,14 +1451,14 @@
       </c>
       <c r="C34" s="4">
         <f>AVERAGE(C2:C5,C11:C17,C23:C28)</f>
-        <v>21.5882352941176</v>
+        <v>21.7058823529412</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C34 C8" formulaRange="1"/>
+    <ignoredError sqref="C8 C34" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1515,7 +1515,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1537,7 +1537,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>20.8333333333333</v>
+        <v>21.5</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -1615,7 +1615,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C20" s="2">
         <f>AVERAGE(C13:C17)</f>
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1670,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C23:C26)</f>
-        <v>18</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C7,C13:C17,C23:C26)</f>
-        <v>20</v>
+        <v>20.4</v>
       </c>
     </row>
   </sheetData>
@@ -1851,10 +1851,10 @@
         <v>47</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1865,7 +1865,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1887,7 +1887,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1909,7 +1909,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1920,7 +1920,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C22" s="2">
         <f>AVERAGE(C12:C19)</f>
-        <v>19.625</v>
+        <v>20.125</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C6,C12:C19,C25:C26)</f>
-        <v>19.2</v>
+        <v>19.4666666666667</v>
       </c>
     </row>
   </sheetData>
